--- a/data_extactor/batch_10_fa/batch_0015_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0015_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Statisticians (آمارشناسان)</t>
+          <t>آمارشناسان (Statisticians)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Database Analyst | Demographer | Education Research Analyst | Mathematical Statistician | Psychometric Consultant | Quantitative Methodologist | Statistical Analyst | Statistical Consultant | Statistical Reporting Analyst | Statistician</t>
+          <t>تحلیل‌گر پایگاه داده | جمعیت‌شناس | تحلیل‌گر پژوهش‌های آموزشی | آماردان ریاضی | مشاور روان‌سنجی | روش‌شناس کمّی | تحلیل‌گر آماری | مشاور آماری | تحلیل‌گر گزارش‌دهی آماری | آماردان</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amazon Redshift | Amazon Web Services AWS software | Angoss KnowledgeSEEKER | Apache Hadoop | Apache Pig | Apache Spark | Aptech Systems GAUSS | Automatic Forecasting Systems Autobox | C++ | Camfit Data Limited Microfit | Common business oriented language COBOL | Cytel StatXact | DataDescription DataDesk | Econometric Software LIMDEP | Extensible markup language XML | Formula translation/translator FORTRAN | GraphPad Software GraphPad Prism | IBM DB2 | IBM SPSS Amos | IBM SPSS AnswerTree | IBM SPSS Statistics | Insightful S-PLUS | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Visual FoxPro | Microsoft Word | Minitab | Muthen &amp; Muthen Mplus | NCR Teradata Warehouse Miner | NCSS Power Analysis and Sample Size PASS | Python | Qlik Tech QlikView | Quantitative Micro Software EViews | R | RAT-STATS | SAP PowerBuilder | نرم‌افزار SAP | SAS | SAS Enterprise Miner | SAS JMP | SAS/CONNECT | STATISTICA | Scientific Software International SSI Hierarchical Linear and Non-Linear Modeling HLM | Scientific Software International SSI LISREL | Stat-Ease Design-Ease | Stat-Ease Design-Expert | StatPoint STATGRAPHICS Centurion | StataCorp Stata | Statistical Solutions BMDP | نرم‌افزار آماری | Structured query language SQL | Sun Microsystems Java | SuperANOVA | Systat Software SigmaPlot | Systat Software SigmaStat | Tableau | Teradata Database | The MathWorks MATLAB | UNISTAT Statistical Package | UNIX | Visual Numerics TS-WAVE | Wolfram Research Mathematica | XGobi | XLISP-STAT</t>
+          <t>Amazon Redshift | نرم‌افزار Amazon Web Services AWS | Angoss KnowledgeSEEKER | Apache Hadoop | Apache Pig | Apache Spark | Aptech Systems GAUSS | Automatic Forecasting Systems Autobox | C++ | Camfit Data Limited Microfit | زبان مشترک تجاری COBOL | Cytel StatXact | DataDescription DataDesk | Econometric Software LIMDEP | زبان نشانه‌گذاری توسعه‌پذیر XML | Formula translation/translator FORTRAN | GraphPad Software GraphPad Prism | IBM DB2 | IBM SPSS Amos | IBM SPSS AnswerTree | IBM SPSS Statistics | Insightful S-PLUS | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Visual FoxPro | Microsoft Word | Minitab | Muthen &amp; Muthen Mplus | NCR Teradata Warehouse Miner | NCSS Power Analysis and Sample Size PASS | Python | Qlik Tech QlikView | Quantitative Micro Software EViews | R | RAT-STATS | SAP PowerBuilder | نرم‌افزار SAP | SAS | SAS Enterprise Miner | SAS JMP | SAS/CONNECT | STATISTICA | Scientific Software International SSI Hierarchical Linear and Non-Linear Modeling HLM | Scientific Software International SSI LISREL | Stat-Ease Design-Ease | Stat-Ease Design-Expert | StatPoint STATGRAPHICS Centurion | StataCorp Stata | Statistical Solutions BMDP | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | SuperANOVA | Systat Software SigmaPlot | Systat Software SigmaStat | Tableau | Teradata Database | The MathWorks MATLAB | UNISTAT Statistical Package | UNIX | Visual Numerics TS-WAVE | Wolfram Research Mathematica | XGobi | XLISP-STAT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخنوری | یادگیری فعال | نوشتار | علوم | راهبردهای یادگیری | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | علوم | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه‌ها و الکترونیک | زبان انگلیسی</t>
+          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | توانایی کار با اعداد | درک نوشتاری | درک شنیداری | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | دید نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | روانی ایده‌ها | حساسیت به مسئله | تشخیص گفتار | خلاقیت | انعطاف‌پذیری بستار</t>
+          <t>استدلال ریاضی | توانایی عددی | درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | روانی ایده‌ها | حساسیت به مسئله | تشخیص گفتار | اصالت | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | اهمیت دقت یا صحت | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای تهویه مطبوع | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>ایمیل | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Bioinformatics Technicians | Biostatisticians | Business Intelligence Analysts | Clinical Data Managers | Computer and Information Research Scientists | Data Scientists | Database Architects | Environmental Economists | Financial Quantitative Analysts | Geneticists | Geographic Information Systems Technologists and Technicians | Health Information Technologists and Medical Registrars | Management Analysts | Mathematicians | Operations Research Analysts | Social Science Research Assistants | Statistical Assistants | Survey Researchers</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | آمارشناسان زیستی | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | دانشمندان تحقیقات کامپیوتر و اطلاعات | دانشمندان داده | معماران پایگاه داده | اقتصاددانان محیط‌زیست | تحلیلگران کمی مالی | ژنتیک‌دان‌ها | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران مدیریت | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | پژوهشگران نظرسنجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biostatisticians (آمارشناسان زیستی)</t>
+          <t>آمارشناسان زیستی (Biostatisticians)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Biometrician | Biostatistical Consultant | Biostatistician | Research Scientist | Statistical Scientist</t>
+          <t>متخصص زیست‌سنجی | مشاور زیست‌آمار | زیست‌آماردان | دانشمند پژوهشی | دانشمند آمار</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bash | C# | C++ | نرم‌افزار پایگاه داده کارآزمایی‌های بالینی | نرم‌افزار تجسم داده‌ها | نرم‌افزار پایگاه داده | Extensible markup language XML | Git | نرم‌افزار گرافیکی | IBM SPSS Statistics | Insightful S-PLUS | JavaScript | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | MySQL | Oracle Database | Oracle Java | PHP | سیستم‌های پایش بیمار | Perl | Python | R | نرم‌افزار S-Plus | نرم‌افزار SAP | SAS | SAS/STAT | STAT! Systems QD Clinical | STATISTICA | Shell script | ابزارهای توسعه نرم‌افزار | StataCorp Stata | نرم‌افزار آماری | Structured query language SQL | The MathWorks MATLAB | Tibco S-PLUS | UNIX | Wolfram Research Mathematica</t>
+          <t>Bash | C# | C++ | نرم‌افزار پایگاه داده کارآزمایی‌های بالینی | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | زبان نشانه‌گذاری توسعه‌پذیر XML | Git | نرم‌افزار گرافیکی | IBM SPSS Statistics | Insightful S-PLUS | JavaScript | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | MySQL | Oracle Database | Oracle Java | PHP | سیستم‌های پایش بیمار | Perl | Python | R | نرم‌افزار S-Plus | نرم‌افزار SAP | SAS | SAS/STAT | STAT! Systems QD Clinical | STATISTICA | Shell script | ابزارهای توسعه نرم‌افزار | StataCorp Stata | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | Tibco S-PLUS | UNIX | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ریاضیات | علوم | سخنوری | درک مطلب | یادگیری فعال | تفکر انتقادی | گوش دادن فعال | نوشتار | راهبردهای یادگیری | نظارت</t>
+          <t>ریاضیات | علوم | سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | گوش دادن فعال | نگارش | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ریاضیات | زبان انگلیسی | رایانه‌ها و الکترونیک | پزشکی و دندانپزشکی</t>
+          <t>ریاضیات | زبان انگلیسی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال استقرایی | درک نوشتاری | بیان شفاهی | استدلال قیاسی | درک شنیداری | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان نوشتاری | توانایی کار با اعداد | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | دید نزدیک | خلاقیت | تجسم | انعطاف‌پذیری بستار | سرعت بستار</t>
+          <t>استدلال ریاضی | استدلال استقرایی | درک کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان کتبی | توانایی عددی | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | تجسم | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقت یا صحت | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | تماس با دیگران</t>
+          <t>ایمیل | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Biochemists and Biophysicists | Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Bioinformatics Technicians | Clinical Data Managers | Clinical Research Coordinators | Data Scientists | Epidemiologists | Financial Quantitative Analysts | Geneticists | Health Informatics Specialists | Mathematicians | Medical Scientists, Except Epidemiologists | Microbiologists | Molecular and Cellular Biologists | Natural Sciences Managers | Operations Research Analysts | Social Science Research Assistants | Statistical Assistants | Statisticians</t>
+          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مدیران داده‌های بالینی | هماهنگ‌کنندگان تحقیقات بالینی | دانشمندان داده | اپیدمیولوژیست‌ها | تحلیلگران کمی مالی | ژنتیک‌دان‌ها | متخصصان انفورماتیک سلامت | ریاضی‌دانان | دانشمندان علوم پزشکی، به جز اپیدمیولوژیست‌ها | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | مدیران علوم طبیعی | تحلیل‌گران تحقیق در عملیات | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Data Scientists (دانشمندان داده)</t>
+          <t>دانشمندان داده (Data Scientists)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Applied Scientist | Data Analyst | Data Science Specialist | Data Scientist | Machine Learning Engineer | Machine Learning Scientist | Quantitative Researcher | Research Data Scientist | Statistical Modeler | Analytics Scientist</t>
+          <t>دانشمند علوم کاربردی | تحلیل‌گر داده | کارشناس علم داده | دانشمند داده | مهندس یادگیری ماشین | دانشمند یادگیری ماشین | پژوهشگر کمّی | دانشمند داده پژوهشی | مدل‌ساز آماری | دانشمند تحلیل داده</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alteryx software | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS SageMaker | Amazon Web Services AWS software | Apache Airflow | Apache Cassandra | Apache Hadoop | Apache Hive | Apache Kafka | Apache MXNet | Apache Pig | Apache Spark | Atlassian Confluence | Atlassian JIRA | Bash | BigQuery | نرم‌افزار هوش تجاری | C | C# | C++ | Docker | Elasticsearch | Flask | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | نرم‌افزار Google Cloud | Google Looker Analytics | IBM SPSS Statistics | JavaScript | JavaScript Object Notation JSON | Jenkins CI | Julia | نرم‌افزار Jupyter | Keras | Kubeflow | Kubernetes | Linux | سیستم‌های اطلاعات مدیریت MIS | نرم‌افزار کلان‌داده MapReduce | نرم‌افزار ریاضی | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Power BI | Microsoft PowerPoint | Microsoft SQL Server | Mlflow | MongoDB | Neo4j | NoSQL | NumPy | OpenAI ChatGPT | Oracle Java | Perl | PostgreSQL | PySpark | PyTorch | Python | Qlik Tech QlikView | R | RESTful API | نرم‌افزار گزارش‌دهی | Ruby | SAS | Scala | SciPy | Scikit-learn | Shell script | Shiny | Snowflake | Splunk Enterprise | StataCorp Stata | نرم‌افزار آماری | Structured query language SQL | Tableau | TensorFlow | Teradata Database | The MathWorks MATLAB | UNIX | XGBoost | pandas | spaCy</t>
+          <t>نرم‌افزار Alteryx | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS SageMaker | نرم‌افزار Amazon Web Services AWS | Apache Airflow | Apache Cassandra | Apache Hadoop | Apache Hive | Apache Kafka | Apache MXNet | Apache Pig | Apache Spark | Atlassian Confluence | Atlassian JIRA | Bash | BigQuery | نرم‌افزار هوش تجاری | C | C# | C++ | Docker | Elasticsearch | Flask | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | نرم‌افزار Google Cloud | Google Looker Analytics | IBM SPSS Statistics | JavaScript | JavaScript Object Notation JSON | Jenkins CI | Julia | نرم‌افزار Jupyter | Keras | Kubeflow | Kubernetes | Linux | سیستم‌های اطلاعات مدیریت MIS | نرم‌افزار کلان‌داده MapReduce | نرم‌افزار ریاضی | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Power BI | Microsoft PowerPoint | Microsoft SQL Server | Mlflow | MongoDB | Neo4j | NoSQL | NumPy | OpenAI ChatGPT | Oracle Java | Perl | PostgreSQL | PySpark | PyTorch | Python | Qlik Tech QlikView | R | RESTful API | نرم‌افزار گزارش‌دهی | Ruby | SAS | Scala | SciPy | Scikit-learn | Shell script | Shiny | Snowflake | Splunk Enterprise | StataCorp Stata | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Tableau | TensorFlow | Teradata Database | The MathWorks MATLAB | UNIX | XGBoost | pandas | spaCy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نوشتار | سخنوری | گوش دادن فعال | علوم | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه‌ها و الکترونیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | اقتصاد و حسابداری | آموزش و پرورش | ارتباطات و رسانه</t>
+          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | اقتصاد و حسابداری | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | حافظه | استدلال ریاضی | توانایی کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقت یا صحت | فشار زمانی | نامه‌ها و یادداشت‌های نوشتاری | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Bioinformatics Technicians | Biostatisticians | Business Intelligence Analysts | Clinical Data Managers | Computer Systems Analysts | Computer and Information Research Scientists | Data Warehousing Specialists | Database Architects | Financial Quantitative Analysts | Geographic Information Systems Technologists and Technicians | Management Analysts | Market Research Analysts and Marketing Specialists | Mathematicians | Operations Research Analysts | Social Science Research Assistants | Statistical Assistants | Statisticians | Survey Researchers</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | آمارشناسان زیستی | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | تحلیلگران سیستم‌های کامپیوتری | دانشمندان تحقیقات کامپیوتر و اطلاعات | متخصصان انبارش داده | معماران پایگاه داده | تحلیلگران کمی مالی | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | آمارشناسان | پژوهشگران نظرسنجی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business Intelligence Analysts (تحلیلگران هوش تجاری)</t>
+          <t>تحلیلگران هوش تجاری (Business Intelligence Analysts)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Business Analyst | Business Intelligence Analyst (BI Analyst) | Business Intelligence Consultant (BI Consultant) | Business Intelligence Coordinator (BI Coordinator) | Business Intelligence Specialist (BI Specialist) | Competitive Intelligence Analyst | Intelligence Analyst | Market Intelligence Analyst | Market Intelligence Consultant | Strategic Business and Technology Intelligence Consultant</t>
+          <t>تحلیل‌گر کسب‌وکار | تحلیل‌گر هوش تجاری (BI) | مشاور هوش تجاری (BI) | هماهنگ‌کننده هوش تجاری (BI) | کارشناس هوش تجاری (BI) | تحلیل‌گر هوشمندی رقابتی | تحلیل‌گر اطلاعاتی | تحلیل‌گر هوشمندی بازار | مشاور هوشمندی بازار | مشاور هوشمندی راهبردی کسب‌وکار و فناوری</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AJAX | Actuate Eclipse BIRT | Adobe Acrobat | Adobe ActionScript | Adobe Dreamweaver | Advanced business application programming ABAP | Airtable | Alteryx software | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Web Services AWS software | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Tomcat | Atlassian Confluence | Atlassian JIRA | Bash | Blackbaud The Raiser's Edge | Business Objects Data Integrator | C | C# | C++ | نرم‌افزار رایانش ابری Citrix | Common business oriented language COBOL | Customer information control system CICS | نرم‌افزار مدل‌سازی داده | نرم‌افزار انبار داده | نرم‌افزار پایگاه داده | Delphi Technology | Django | Drupal | Dynamic hypertext markup language DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eko | Elasticsearch | Enterprise JavaBeans | Epic Systems | Ext JS | Extensible hypertext markup language XHTML | Extensible markup language XML | Facebook | FileMaker Pro | نرم‌افزار حسابداری وجوه | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Ads | Google Analytics | Google Docs | Google Looker Analytics | Google Sites | Google Slides | Healthcare common procedure coding system HCPCS | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | Hypertext markup language HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IBM Unica Enterprise | IBM WebSphere | Informatica Data Explorer | نرم‌افزار Informatica | Information Builders WebFOCUS | نرم‌افزار محیط توسعه یکپارچه IDE | JavaScript | JavaScript Object Notation JSON | Job control language JCL | Jupyter Notebook | KornShell | LexisNexis | Linux | نرم‌افزار MEDITECH | Marketo Marketing Automation | McAfee | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه پزشکی | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power Automate | Microsoft Power BI | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Proclarity | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | NetSuite ERP | NoSQL | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | نرم‌افزار Oracle Cloud | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Essbase | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle SQL Developer | Oracle Siebel Marketing Resource Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | PTC Creo Parametric | Panorama NovaView | Perl | PostgreSQL | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار گزارش‌دهی | Rogue Wave Software IMSL Numerical Libraries | Ruby | Ruby on Rails | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | SAP ERP | SAP NetWeaver BW | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Shell script | SiSense Prism | Skype | Snowflake | Splunk Enterprise | StataCorp Stata | Structured query language SQL | Swift | Tableau | نرم‌افزار مالی | Teradata Database | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | Unified modeling language UML | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Wireshark | YouTube | jQuery</t>
+          <t>AJAX | Actuate Eclipse BIRT | Adobe Acrobat | Adobe ActionScript | Adobe Dreamweaver | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | نرم‌افزار Alteryx | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Tomcat | Atlassian Confluence | Atlassian JIRA | Bash | Blackbaud The Raiser's Edge | Business Objects Data Integrator | C | C# | C++ | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار مدل‌سازی داده | نرم‌افزار انبار داده | نرم‌افزار پایگاه داده | Delphi Technology | Django | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eko | Elasticsearch | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | FileMaker Pro | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Ads | Google Analytics | Google Docs | Google Looker Analytics | Google Sites | Google Slides | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IBM Unica Enterprise | IBM WebSphere | Informatica Data Explorer | نرم‌افزار Informatica | Information Builders WebFOCUS | نرم‌افزار محیط توسعه یکپارچه IDE | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LexisNexis | Linux | نرم‌افزار MEDITECH | Marketo Marketing Automation | McAfee | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power Automate | Microsoft Power BI | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Proclarity | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows Server | Microsoft Word | Minitab | MongoDB | MySQL | Nagios | NetSuite ERP | NoSQL | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Cloud software | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Essbase | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle SQL Developer | Oracle Siebel Marketing Resource Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | PTC Creo Parametric | Panorama NovaView | Perl | PostgreSQL | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار گزارش‌دهی | Rogue Wave Software IMSL Numerical Libraries | Ruby | Ruby on Rails | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | SAP ERP | SAP NetWeaver BW | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Shell script | SiSense Prism | Skype | Snowflake | Splunk Enterprise | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Swift | Tableau | نرم‌افزار مالیاتی | Teradata Database | The MathWorks MATLAB | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | Veritas NetBackup | نرم‌افزار شبکه خصوصی مجازی VPN | Wireshark | YouTube | jQuery</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخنوری | تفکر انتقادی | یادگیری فعال | نوشتار | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه‌ها و الکترونیک | ریاضیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | اقتصاد و حسابداری</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | استدلال ریاضی | روانی ایده‌ها | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری بستار | دید نزدیک | خلاقیت | توانایی کار با اعداد</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | استدلال ریاضی | روانی ایده‌ها | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری بستار | بینایی نزدیک | اصالت | توانایی عددی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | اهمیت دقت یا صحت | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای تهویه مطبوع | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Blockchain Engineers | Clinical Data Managers | Computer Systems Analysts | Computer Systems Engineers/Architects | Computer and Information Systems Managers | Data Scientists | Data Warehousing Specialists | Database Administrators | Database Architects | Document Management Specialists | Financial Quantitative Analysts | Financial Risk Specialists | Management Analysts | Market Research Analysts and Marketing Specialists | Marketing Managers | Operations Research Analysts | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Search Marketing Strategists | Software Developers | Statistical Assistants</t>
+          <t>مهندسان بلاک‌چین | مدیران داده‌های بالینی | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیلگران کمی مالی | متخصصان ریسک مالی | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | تحلیل‌گران تحقیق در عملیات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | استراتژیست‌های بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | دستیاران آماری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clinical Data Managers (مدیران داده‌های بالینی)</t>
+          <t>مدیران داده‌های بالینی (Clinical Data Managers)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clinical Data Management Director (CDM Director) | Clinical Data Management Manager (CDM Manager) | Clinical Data Manager | Clinical Informatics Manager | Data Deliverables Manager | Data Management Manager</t>
+          <t>مدیر ارشد مدیریت داده‌های بالینی (CDM) | مدیر مدیریت داده‌های بالینی (CDM) | مدیر داده‌های بالینی | مدیر انفورماتیک بالینی | مدیر خروجی‌های داده | مدیر مدیریت داده</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5AM Glassbox Translational Research | نرم‌افزار اتوماسیون مراقبت‌های بهداشتی Allscripts | Autocoders | C# | C++ | نرم‌افزار رایانش ابری Citrix | ClearTrial | نرم‌افزار مدیریت کارآزمایی بالینی | DZS Software Solutions ClinPlus | نرم‌افزار کدگذاری دارو | نرم‌افزار ضبط داده‌های الکترونیکی EDC | Epic Systems | نرم‌افزار سوابق پزشکی الکترونیکی EpicCare Ambulatory | Extensible markup language XML | Fortress Medical Clindex | Go | IBM SPSS Statistics | InforSense InforSense | سیستم مدیریت ePRO Invivo Data EPX | KIKA Veracity | نرم‌افزار MEDITECH | Medidata Rave Data Management | Merge Healthcare eTrials | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | OpenClinica | Oracle Clinical | Oracle Java | Oracle Remote Data Capture | Oracle SQL Loader | PPD eLoader | نرم‌افزار ردیابی بیمار | PercipEnz Technologies OnCore-Clinical Research Management OnCore-CRM | Phase Forward Clintrial | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار پایگاه داده رابطه‌ای | SAP BusinessObjects Crystal Reports | SAP Crystal Reports | SAS | SAS JMP | Sierra Scientific Software CRIS | Structured query language SQL | StudyManager Sponsor Edition | SyMetric Sciences SyMetric | TOPAZ Enterprise Software Suite | Teradata Database | ePharmaSolutions eMVR</t>
+          <t>5AM Glassbox Translational Research | نرم‌افزار اتوماسیون مراقبت‌های بهداشتی Allscripts | Autocoders | C# | C++ | نرم‌افزار رایانش ابری Citrix | ClearTrial | نرم‌افزار مدیریت کارآزمایی بالینی | DZS Software Solutions ClinPlus | نرم‌افزار کدگذاری دارو | نرم‌افزار ضبط الکترونیکی داده EDC | Epic Systems | نرم‌افزار سوابق پزشکی الکترونیکی EpicCare Ambulatory | زبان نشانه‌گذاری توسعه‌پذیر XML | Fortress Medical Clindex | Go | IBM SPSS Statistics | InforSense InforSense | Invivo Data EPX ePRO Management System | KIKA Veracity | نرم‌افزار MEDITECH | Medidata Rave Data Management | Merge Healthcare eTrials | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Word | OpenClinica | Oracle Clinical | Oracle Java | Oracle Remote Data Capture | Oracle SQL Loader | PPD eLoader | نرم‌افزار ردیابی بیمار | PercipEnz Technologies OnCore-Clinical Research Management OnCore-CRM | Phase Forward Clintrial | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار پایگاه داده رابطه‌ای | SAP BusinessObjects Crystal Reports | SAP Crystal Reports | SAS | SAS JMP | Sierra Scientific Software CRIS | زبان پرس‌وجوی ساختاریافته SQL | StudyManager Sponsor Edition | SyMetric Sciences SyMetric | TOPAZ Enterprise Software Suite | Teradata Database | ePharmaSolutions eMVR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنوری | درک مطلب | گوش دادن فعال | نوشتار | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه‌ها و الکترونیک | خدمات مشتری و شخصی | ریاضیات | پزشکی و دندانپزشکی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شنیداری | درک نوشتاری | بیان شفاهی | دید نزدیک | بیان نوشتاری | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی کار با اعداد | روانی ایده‌ها | توجه انتخابی | خلاقیت</t>
+          <t>استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | روانی ایده‌ها | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | اهمیت دقت یا صحت | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای تهویه مطبوع | تماس با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار وظایف مشابه | آزادی در تصمیم‌گیری</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Bioinformatics Technicians | Biostatisticians | Business Intelligence Analysts | Clinical Research Coordinators | Data Scientists | Database Administrators | Document Management Specialists | Health Informatics Specialists | Health Information Technologists and Medical Registrars | Management Analysts | Medical Records Specialists | Medical and Health Services Managers | Natural Sciences Managers | Project Management Specialists | Regulatory Affairs Specialists | Social Science Research Assistants | Statistical Assistants | Statisticians</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | آمارشناسان زیستی | تحلیلگران هوش تجاری | هماهنگ‌کنندگان تحقیقات بالینی | دانشمندان داده | مدیران پایگاه داده | متخصصان مدیریت اسناد | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | مدیران خدمات پزشکی و بهداشتی | مدیران علوم طبیعی | متخصصان مدیریت پروژه | متخصصان امور نظارتی | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mathematical Science Occupations, All Other (مشاغل علوم ریاضی، سایر)</t>
+          <t>مشاغل علوم ریاضی، سایر (Mathematical Science Occupations, All Other)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Applied Mathematician | Applied Statistician | Computational Scientist | Cryptanalyst | Decision Scientist | Mathematical Modeler | Mathematical Statistician | Numerical Analyst | Optimization Analyst | Quantitative Analyst</t>
+          <t>ریاضی‌دان کاربردی | آماردان کاربردی | دانشمند محاسباتی | تحلیل‌گر رمز | دانشمند علم تصمیم | مدل‌ساز ریاضی | آماردان ریاضی | تحلیل‌گر عددی | تحلیلگر بهینه‌سازی | تحلیل‌گر کمّی</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Structured query language SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | نرم‌افزار پایگاه داده | Microsoft Word | نرم‌افزار ایمیل | Microsoft PowerPoint | نرم‌افزار مرورگر وب</t>
+          <t>Microsoft Excel | زبان پرس‌وجوی ساختاریافته SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | نرم‌افزار پایگاه داده | Microsoft Word | نرم‌افزار ایمیل | Microsoft PowerPoint | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نوشتار | سخنوری | گوش دادن فعال | علوم | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه‌ها و الکترونیک | زبان انگلیسی | فیزیک | مهندسی و فناوری | اقتصاد و حسابداری | آموزش و پرورش | مدیریت و اداره</t>
+          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | فیزیک | مهندسی و فناوری | اقتصاد و حسابداری | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | حافظه | استدلال ریاضی | توانایی کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقت یا صحت | فشار زمانی | نامه‌ها و یادداشت‌های نوشتاری | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Bioinformatics Technicians | Actuaries | Mathematicians | Operations Research Analysts | Statisticians | Biostatisticians | Data Scientists | Business Intelligence Analysts | Clinical Data Managers | Financial Quantitative Analysts | Computer and Information Research Scientists | Computer Programmers | Software Developers | Database Architects | Economists | Financial and Investment Analysts | Market Research Analysts and Marketing Specialists | Natural Sciences Managers | Physicists | Mathematical Science Teachers, Postsecondary</t>
+          <t>تکنسین‌های بیوانفورماتیک | کارشناسان آمار بیمه (اکچوئری) | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | آمارشناسان | آمارشناسان زیستی | دانشمندان داده | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | تحلیلگران کمی مالی | دانشمندان تحقیقات کامپیوتر و اطلاعات | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان نرم‌افزار | معماران پایگاه داده | اقتصاددانان | تحلیلگران مالی و سرمایه‌گذاری | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران علوم طبیعی | فیزیکدانان | مدرسان علوم ریاضی، پس از متوسطه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bioinformatics Technicians (تکنسین‌های بیوانفورماتیک)</t>
+          <t>تکنسین‌های بیوانفورماتیک (Bioinformatics Technicians)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bioinformatics Analyst | Bioinformatics Specialist | Bioinformatics Technician | Biotechnician | Museum Informatics Specialist | Research Scientist | Scientific Informatics Analyst</t>
+          <t>تحلیل‌گر زیست‌اطلاعاتی | کارشناس زیست‌اطلاعاتی | تکنسین زیست‌اطلاعاتی | تکنسین زیست‌فناوری | کارشناس انفورماتیک موزه | دانشمند پژوهشی | تحلیل‌گر انفورماتیک علمی</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apache Subversion SVN | Atlassian Bamboo | Avaya Identity Engines | ابزار جستجوی هم‌ترازی محلی پایه BLAST | Bioconductor | Bowtie | Burrows-Wheeler Aligner BWA | C | C++ | ClustalW | Cufflinks | نرم‌افزار تجسم داده‌ها | Esri ArcGIS | GENSCAN | Genome Analysis Toolkit GATK | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | Hypertext markup language HTML | IBM SPSS Statistics | Jenkins CI | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | MySQL | Oracle Database | Oracle Java | PHYLIP | Perl | Python | R | Ruby | نرم‌افزار SAP | SAS | Structured query language SQL | The MathWorks MATLAB | Thermo Fisher Scientific Ion Reporter | TopHat | نرم‌افزار سیستم پروتکل صوتی روی اینترنت VoIP | نرم‌افزار مرورگر وب</t>
+          <t>Apache Subversion SVN | Atlassian Bamboo | Avaya Identity Engines | ابزار Basic Local Alignment Search Tool BLAST | Bioconductor | Bowtie | Burrows-Wheeler Aligner BWA | C | C++ | ClustalW | Cufflinks | نرم‌افزار تجسم داده | Esri ArcGIS | GENSCAN | Genome Analysis Toolkit GATK | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | زبان نشانه‌گذاری ابرمتن HTML | IBM SPSS Statistics | Jenkins CI | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | MySQL | Oracle Database | Oracle Java | PHYLIP | Perl | Python | R | Ruby | نرم‌افزار SAP | SAS | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | Thermo Fisher Scientific Ion Reporter | TopHat | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتار | تفکر انتقادی | یادگیری فعال | سخنوری | ریاضیات | نظارت | علوم</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | سخن گفتن | ریاضیات | نظارت | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>رایانه‌ها و الکترونیک | ریاضیات | زبان انگلیسی | زیست‌شناسی</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شنیداری | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | ترتیب‌دهی اطلاعات | استدلال ریاضی | توجه انتخابی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری بستار | روانی ایده‌ها | توانایی کار با اعداد | خلاقیت | تجسم | سرعت ادراکی</t>
+          <t>درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی | توجه انتخابی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | روانی ایده‌ها | توانایی عددی | اصالت | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای تهویه مطبوع | اهمیت دقت یا صحت | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>ایمیل | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bioengineers and Biomedical Engineers | Bioinformatics Scientists | Biological Technicians | Biostatisticians | Clinical Data Managers | Computer and Information Research Scientists | Cytogenetic Technologists | Data Scientists | Database Administrators | Database Architects | Geographic Information Systems Technologists and Technicians | Health Information Technologists and Medical Registrars | Medical Records Specialists | Medical and Clinical Laboratory Technologists | Molecular and Cellular Biologists | Nanotechnology Engineering Technologists and Technicians | Natural Sciences Managers | Social Science Research Assistants | Statistical Assistants | Statisticians</t>
+          <t>مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های زیستی | آمارشناسان زیستی | مدیران داده‌های بالینی | دانشمندان تحقیقات کامپیوتر و اطلاعات | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | متخصصان مدارک پزشکی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Architects, Except Landscape and Naval (معماران، به‌جز منظر و دریایی)</t>
+          <t>معماران، به‌جز منظر و دریایی (Architects, Except Landscape and Naval)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Architect | Design Architect | Planner | Project Architect | Specifications Writer</t>
+          <t>معمار | معمار طراح | برنامه‌ریز | معمار پروژه | تدوین‌کننده مشخصات فنی</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1ST Pricing Window &amp; Door Toolkit | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Web Services AWS software | Apache Cassandra | Apache Hadoop | Apache Hive | Apache Maven | Apache Pig | Applied Search Technology CADFind | Artifice DesignWorkshop | AutoDesSys form Z | Autodesk 3ds Max Design | Autodesk Architectural Studio | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | AzTechSoft GPS2CAD | BQE Software ArchiOffice | BeamChek | Bentley MicroStation | Chaos Enscape | Chef | نرم‌افزار طراحی و نقشه‌کشی به کمک رایانه CADD | Craftsman CD Estimator | نرم‌افزار پایگاه داده | Drcauto Smart Architect LT Pro | نرم‌افزار ESRI ArcGIS | FEMA EMMIE | FileNet P8 | Graphisoft ArchiCAD | Intuit QuickBooks | McNeel Rhinoceros 3D | Micro-Press MicroStation PowerDraft | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Word | MongoDB | MyFamilySoftware Instant Architect | NavisWorks Jetstream | NoSQL | Oracle JDBC | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PostgreSQL | Puppet | Qlik Tech QlikView | Quality Plans &amp; Software HVAC Calculator | نرم‌افزار نشر سازمانی Quark | Quest Erwin Data Modeler | Roof Builder Tools | Trimble SketchUp Pro | Turtle Creek Software Goldenseal | Turtle Creek Software Goldenseal (ویژگی حسابداری) | Turtle Creek Software Goldenseal (ویژگی تقویم و زمان‌بندی) | Turtle Creek Software Goldenseal (ویژگی حسابداری زمان) | VectorWorks ARCHITECT | Verilog | نرم‌افزار زبان مدل‌سازی واقعیت مجازی VRML</t>
+          <t>1ST Pricing Window &amp; Door Toolkit | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | نرم‌افزار Amazon Web Services AWS | Apache Cassandra | Apache Hadoop | Apache Hive | Apache Maven | Apache Pig | Applied Search Technology CADFind | Artifice DesignWorkshop | AutoDesSys form Z | Autodesk 3ds Max Design | Autodesk Architectural Studio | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | AzTechSoft GPS2CAD | BQE Software ArchiOffice | BeamChek | Bentley MicroStation | Chaos Enscape | Chef | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Craftsman CD Estimator | نرم‌افزار پایگاه داده | Drcauto Smart Architect LT Pro | نرم‌افزار ESRI ArcGIS | FEMA EMMIE | FileNet P8 | Graphisoft ArchiCAD | Intuit QuickBooks | McNeel Rhinoceros 3D | Micro-Press MicroStation PowerDraft | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Word | MongoDB | MyFamilySoftware Instant Architect | NavisWorks Jetstream | NoSQL | Oracle JDBC | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PostgreSQL | Puppet | Qlik Tech QlikView | Quality Plans &amp; Software HVAC Calculator | نرم‌افزار نشر سازمانی Quark | Quest Erwin Data Modeler | Roof Builder Tools | Trimble SketchUp Pro | Turtle Creek Software Goldenseal | Turtle Creek Software Goldenseal (ویژگی حسابداری) | Turtle Creek Software Goldenseal (ویژگی تقویم و زمان‌بندی) | Turtle Creek Software Goldenseal (ویژگی حسابداری زمان) | VectorWorks ARCHITECT | Verilog | نرم‌افزار زبان مدل‌سازی واقعیت مجازی VRML</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخنوری | گوش دادن فعال | نوشتار | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مهندسی و فناوری | رایانه‌ها و الکترونیک | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | مکانیک | ریاضیات | اقتصاد و حسابداری | فروش و بازاریابی | هنرهای زیبا | فیزیک | تولید و پردازش | آموزش و پرورش | پرسنل و منابع انسانی</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | مکانیک | ریاضیات | اقتصاد و حسابداری | فروش و بازاریابی | هنرهای زیبا | فیزیک | تولید و فرآوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم | بیان شفاهی | بیان نوشتاری | روانی ایده‌ها | خلاقیت | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید نزدیک | دید دور | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توانایی کار با اعداد | استدلال ریاضی | سرعت ادراکی | توجه انتخابی | سرعت بستار</t>
+          <t>تجسم | بیان شفاهی | بیان کتبی | روانی ایده‌ها | اصالت | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | بینایی دور | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | سرعت ادراکی | توجه انتخابی | سرعت بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | صرف زمان برای نشستن | محیط داخلی، دارای تهویه مطبوع | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقت یا صحت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارکنان | نامه‌ها و یادداشت‌های نوشتاری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Architectural and Civil Drafters | Architectural and Engineering Managers | Architecture Teachers, Postsecondary | Civil Engineering Technologists and Technicians | Civil Engineers | Commercial and Industrial Designers | Construction Managers | Construction and Building Inspectors | Electrical and Electronics Drafters | Facilities Managers | First-Line Supervisors of Construction Trades and Extraction Workers | Industrial Engineers | Interior Designers | Landscape Architects | Maintenance and Repair Workers, General | Project Management Specialists | Solar Energy Installation Managers | Solar Energy Systems Engineers | Sustainability Specialists | Wind Energy Development Managers</t>
+          <t>نقشه‌کشان معماری و عمران | مدیران معماری و مهندسی | مدرسان معماری، پس از متوسطه | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | طراحان تجاری و صنعتی | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | نقشه‌کشان برق و الکترونیک | مدیران تسهیلات | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | مهندسان صنایع | طراحان داخلی | معماران منظر | کارگران نگهداری و تعمیرات عمومی | متخصصان مدیریت پروژه | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | متخصصان پایداری | مدیران توسعه انرژی بادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Landscape Architects (معماران منظر)</t>
+          <t>معماران منظر (Landscape Architects)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AP BD+C (Accredited Professional in Building Design and Construction) | Golf Course Architect | Land Planner | Landscape Architect | Landscape Designer | Landscape Planner | Park Planner | Planner | Professional Landscape Architect (PLA) | Project Landscape Architect</t>
+          <t>AP BD+C (متخصص دارای گواهی طراحی و ساخت ساختمان) | معمار زمین گلف | برنامه‌ریز کاربری زمین | معمار منظر | طراح منظر | برنامه‌ریز منظر | برنامه‌ریز پارک | برنامه‌ریز | معمار حرفه‌ای منظر (PLA) | معمار منظر پروژه</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk 3ds Max | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley MicroStation | Corel CorelDraw Graphics Suite | Coyote Software DynaSCAPE Design | نرم‌افزار ESRI ArcGIS | ESRI ArcView | سیستم‌های اطلاعات جغرافیایی GIS | Lumion | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Trimble SketchUp Pro | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk 3ds Max | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley MicroStation | Corel CorelDraw Graphics Suite | Coyote Software DynaSCAPE Design | نرم‌افزار ESRI ArcGIS | ESRI ArcView | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Lumion | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Trimble SketchUp Pro | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخنوری | تفکر انتقادی | نوشتار | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و ساخت‌وساز | جغرافیا | زبان انگلیسی | مهندسی و فناوری | خدمات مشتری و شخصی | رایانه‌ها و الکترونیک | ایمنی و امنیت عمومی | زیست‌شناسی | مدیریت و اداره | قانون و دولت | ریاضیات | حمل‌ونقل</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | جغرافیا | زبان انگلیسی | مهندسی و فناوری | خدمات مشتری و شخصی | رایانه و الکترونیک | ایمنی و امنیت عمومی | زیست‌شناسی | مدیریت و اداره | قانون و دولت | ریاضیات | حمل و نقل</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | خلاقیت | تجسم | بیان نوشتاری | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | دید دور | توانایی کار با اعداد | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | اصالت | تجسم | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | بینایی دور | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای تهویه مطبوع | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | تماس با دیگران | اهمیت دقت یا صحت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | نامه‌ها و یادداشت‌های نوشتاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | ارتباط با دیگران | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Agricultural Engineers | Architects, Except Landscape and Naval | Architectural and Civil Drafters | Architecture Teachers, Postsecondary | Brownfield Redevelopment Specialists and Site Managers | Chief Sustainability Officers | Civil Engineering Technologists and Technicians | Civil Engineers | Conservation Scientists | Construction Managers | Environmental Restoration Planners | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | Industrial Ecologists | Interior Designers | Range Managers | Solar Energy Installation Managers | Surveying and Mapping Technicians | Sustainability Specialists | Urban and Regional Planners | Water Resource Specialists</t>
+          <t>مهندسان کشاورزی | معماران، به‌جز منظر و دریایی | نقشه‌کشان معماری و عمران | مدرسان معماری، پس از متوسطه | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | دانشمندان حفاظت | مدیران ساخت‌وساز | برنامه‌ریزان احیای محیط‌زیست | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | بوم‌شناسان صنعتی | طراحان داخلی | مدیران مراتع | مدیران نصب انرژی خورشیدی | تکنسین‌های نقشه‌برداری و نقشه‌کشی | متخصصان پایداری | برنامه‌ریزان شهری و منطقه‌ای | متخصصان منابع آب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cartographers and Photogrammetrists (نقشه‌برداران و فتوگرامتریست‌ها)</t>
+          <t>نقشه‌برداران و فتوگرامتریست‌ها (Cartographers and Photogrammetrists)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aerial Photogrammetrist | Cartographer | Cartographic Designer | Digital Cartographer | Mapper | Photogrammetric Technician | Photogrammetrist | Stereo Compiler | Stereoplotter Operator</t>
+          <t>متخصص فتوگرامتری هوایی | نقشه‌نگار | طراح نقشه | نقشه‌نگار دیجیتال | نقشه‌بردار | تکنسین فتوگرامتری | متخصص فتوگرامتری | تدوین‌گر تصاویر استریو | اپراتور استریوپلاتر</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | نرم‌افزار تنظیم آیروتری‌انگولاسیون | Aldus FreeHand | Arbor Image Draftsman | Autodesk AutoCAD | Autodesk World | Bentley MicroStation | Bentley Systems InRoads Suite | Boeing Kork Digital Mapping | Boeing SoftPlotter | C | Corel CorelDraw Graphics Suite | Corporate Montage CADScript | Cosmo Software Cosmo World | پایگاه‌های داده دیجیتال | نرم‌افزار نقشه‌برداری دیجیتال | ERDAS ER Mapper | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | نرم‌افزار ESRI | نرم‌افزار ایمیل | Extensible markup language XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | Hexagon Intergraph | IBM iSeries Access | نرم‌افزار تحلیل تصویر | نرم‌افزار پردازش تصویر | Intergraph ImageStation Stereo Softcopy Kit SSK | JavaScript Object Notation JSON | Leica AEROPLAN LiDAR | MapInfo | نرم‌افزار نقشه‌برداری | Mapthematics GeoCart | Master Seafloor Digital Database | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | MultiGen Paradigm Vega Prime | Oracle Database | نرم‌افزار پگینگ آیروتری‌انگولاسیون تحلیلی دقیق | Python | Quark Immedia | QuarkXPress | RSI ENVI | Rand McNally World Digital Database | RockWare ArcMap | SAP Adaptive Server Enterprise | نرم‌افزار SAP | ابزارهای توسعه نرم‌افزار | Standardized general markup language SGML | نرم‌افزار استریوپلاتر | Structured query language SQL | Terrasolid TerraScan | Textron Systems Geospatial Solutions RemoteView | World Vector Shoreline</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | نرم‌افزار تنظیم آیروتری‌انگولاسیون | Aldus FreeHand | Arbor Image Draftsman | Autodesk AutoCAD | Autodesk World | Bentley MicroStation | Bentley Systems InRoads Suite | Boeing Kork Digital Mapping | Boeing SoftPlotter | C | Corel CorelDraw Graphics Suite | Corporate Montage CADScript | Cosmo Software Cosmo World | پایگاه‌های داده دیجیتال | نرم‌افزار نقشه‌برداری دیجیتال | ERDAS ER Mapper | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | نرم‌افزار ESRI | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | Hexagon Intergraph | IBM iSeries Access | نرم‌افزار تحلیل تصویر | نرم‌افزار پردازش تصویر | Intergraph ImageStation Stereo Softcopy Kit SSK | JavaScript Object Notation JSON | Leica AEROPLAN LiDAR | MapInfo | نرم‌افزار نقشه‌برداری | Mapthematics GeoCart | Master Seafloor Digital Database | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | MultiGen Paradigm Vega Prime | Oracle Database | نرم‌افزار پگینگ آیروتری‌انگولاسیون تحلیلی دقیق | Python | Quark Immedia | QuarkXPress | RSI ENVI | Rand McNally World Digital Database | RockWare ArcMap | SAP Adaptive Server Enterprise | نرم‌افزار SAP | ابزارهای توسعه نرم‌افزار | Standardized general markup language SGML | نرم‌افزار استریوپلاتر | زبان پرس‌وجوی ساختاریافته SQL | Terrasolid TerraScan | Textron Systems Geospatial Solutions RemoteView | World Vector Shoreline</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نوشتار | گوش دادن فعال | یادگیری فعال | سخنوری | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | رایانه‌ها و الکترونیک | زبان انگلیسی | طراحی | ریاضیات</t>
+          <t>جغرافیا | رایانه و الکترونیک | زبان انگلیسی | طراحی | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک نوشتاری | دید نزدیک | درک شنیداری | استدلال استقرایی | بیان نوشتاری | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | تجسم | دید دور | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | خلاقیت | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | استدلال ریاضی</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | استدلال استقرایی | بیان کتبی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | تجسم | بینایی دور | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | اصالت | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای تهویه مطبوع | ایمیل | اهمیت دقت یا صحت | صرف زمان برای نشستن | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | تماس با دیگران | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف مشابه | صرف زمان برای انجام حرکات تکراری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Architectural and Civil Drafters | Atmospheric and Space Scientists | Calibration Technologists and Technicians | Civil Engineering Technologists and Technicians | Data Scientists | Data Warehousing Specialists | Database Architects | Electrical and Electronics Drafters | Geodetic Surveyors | Geographers | Geographic Information Systems Technologists and Technicians | Geological Technicians, Except Hydrologic Technicians | Geoscientists, Except Hydrologists and Geographers | Hydrologic Technicians | Remote Sensing Scientists and Technologists | Remote Sensing Technicians | Software Developers | Statistical Assistants | Surveying and Mapping Technicians | Surveyors</t>
+          <t>نقشه‌کشان معماری و عمران | دانشمندان علوم جوی و فضایی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی عمران | دانشمندان داده | متخصصان انبارش داده | معماران پایگاه داده | نقشه‌کشان برق و الکترونیک | نقشه‌برداران ژئودتیک | جغرافیدانان | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌برداران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0015_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0015_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | علوم پایه | راهبردهای یادگیری | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | علوم | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | محاسبات عددی | درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | دید نزدیک | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | وضوح گفتار | روانی کلام و سیالی ایده‌ها | حساسیت به مسئله | تشخیص گفتار | ابتکار و اصالت | تفکیک الگو و انعطاف شکل پایانی</t>
+          <t>استدلال ریاضی | توانایی عددی | درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | بینایی نزدیک | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | روانی ایده‌ها | حساسیت به مسئله | تشخیص گفتار | اصالت | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مهندسان زیست‌پزشکی و بیوالکتریک | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | دانشمندان علوم رایانه و پژوهشگران اطلاعات | دانشمندان علوم داده | معماران پایگاه داده | اقتصاددانان محیط زیست | تحلیل‌گران کمی مسائل مالی | ژنتیک‌دانان | تکنسین‌ها و متخصصان سیستم‌های اطلاعات جغرافیایی GIS | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | ریاضیدانان | تحلیل‌گران تحقیق در عملیات | کارشناسان پژوهش‌های علوم اجتماعی | تکنسین‌های آمار | پژوهشگران افکارسنجی و پیمایشی</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | پژوهشگران علوم رایانه و اطلاعات | دانشمندان داده | معماران پایگاه داده | اقتصاددانان محیط زیست | تحلیل‌گران کمّی مالی | متخصصان ژنتیک | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان تحلیل مدیریت و روش‌ها | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ریاضیات | علوم پایه | سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | شنیدن فعال | نگارش | راهبردهای یادگیری | نظارت</t>
+          <t>ریاضیات | علوم | سخن گفتن | درک مطلب | یادگیری فعال | تفکر انتقادی | گوش دادن فعال | نگارش | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | استدلال استقرایی | درک کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | بیان کتبی | محاسبات عددی | تشخیص گفتار | روانی کلام و سیالی ایده‌ها | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | ابتکار و اصالت | تجسم فضایی | تفکیک الگو و انعطاف شکل پایانی | سرعت درک الگو و انسجام</t>
+          <t>استدلال ریاضی | استدلال استقرایی | درک کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان کتبی | توانایی عددی | تشخیص گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | تجسم | انعطاف‌پذیری بستار | سرعت بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیست‌پزشکی و بیوالکتریک | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مدیران داده‌های بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان علوم داده | اپیدمیولوژیست‌ها | تحلیل‌گران کمی مسائل مالی | ژنتیک‌دانان | متخصصان انفورماتیک سلامت | ریاضیدانان | دانشمندان علوم پزشکی، به‌جز اپیدمیولوژیست‌ها | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مدیران علوم پایه | تحلیل‌گران تحقیق در عملیات | کارشناسان پژوهش‌های علوم اجتماعی | تکنسین‌های آمار | کارشناسان آمار</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مدیران داده‌های بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان داده | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | تحلیل‌گران کمّی مالی | متخصصان ژنتیک | متخصصان انفورماتیک سلامت | ریاضی‌دانان | پژوهشگران و دانشمندان علوم پزشکی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | مدیران علوم طبیعی و پایه‌ای | تحلیل‌گران تحقیق در عملیات | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و امور اداری | اقتصاد و حسابداری | آموزش و یادگیری | ارتباطات و رسانه</t>
+          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | مهندسی و فناوری | مدیریت و اداره | اقتصاد و حسابداری | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه و مدیریت هم‌زمان وظایف | تجسم فضایی | به‌خاطرسپاری | استدلال ریاضی | محاسبات عددی | سرعت درک | تفکیک الگو و انعطاف شکل پایانی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان زیست‌پزشکی و بیوالکتریک | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های رایانه‌ای | دانشمندان علوم رایانه و پژوهشگران اطلاعات | متخصصان انبارهای داده | معماران پایگاه داده | تحلیل‌گران کمی مسائل مالی | تکنسین‌ها و متخصصان سیستم‌های اطلاعات جغرافیایی GIS | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | کارشناسان تحلیل بازار و بازاریابی | ریاضیدانان | تحلیل‌گران تحقیق در عملیات | کارشناسان پژوهش‌های علوم اجتماعی | تکنسین‌های آمار | کارشناسان آمار | پژوهشگران افکارسنجی و پیمایشی</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | پژوهشگران علوم رایانه و اطلاعات | متخصصان انباره داده | معماران پایگاه داده | تحلیل‌گران کمّی مالی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | کارشناسان آمار | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری</t>
+          <t>رایانه و الکترونیک | ریاضیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | وضوح گفتار | استدلال ریاضی | روانی کلام و سیالی ایده‌ها | تشخیص گفتار | حساسیت به مسئله | تفکیک الگو و انعطاف شکل پایانی | دید نزدیک | ابتکار و اصالت | محاسبات عددی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | استدلال ریاضی | روانی ایده‌ها | تشخیص گفتار | حساسیت به مسئله | انعطاف‌پذیری بستار | بینایی نزدیک | اصالت | توانایی عددی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های رایانه‌ای | معماران و مهندسان سیستم‌های رایانه‌ای | مدیران سیستم‌های اطلاعاتی و فناوری اطلاعات | دانشمندان علوم داده | متخصصان انبارهای داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد و مدارک | تحلیل‌گران کمی مسائل مالی | کارشناسان مدیریت ریسک مالی | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | کارشناسان تحلیل بازار و بازاریابی | مدیران بازاریابی | تحلیل‌گران تحقیق در عملیات | کارشناسان فروش خدمات تخصصی | استراتژیست‌های بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | تکنسین‌های آمار</t>
+          <t>مهندسان زنجیره بلوکی | مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | تحلیل‌گران تحقیق در عملیات | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ریاضیات | پزشکی و دندان‌پزشکی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | ریاضیات | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | انعطاف‌پذیری در دسته‌بندی | تفکیک الگو و انعطاف شکل پایانی | محاسبات عددی | روانی کلام و سیالی ایده‌ها | توجه انتخابی | ابتکار و اصالت</t>
+          <t>استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | روانی ایده‌ها | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان زیست‌پزشکی و بیوالکتریک | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان علوم داده | مدیران پایگاه داده | متخصصان مدیریت اسناد و مدارک | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران سیستم‌ها و روش‌های مدیریتی | کارشناسان مدارک و سوابق پزشکی | مدیران خدمات بهداشتی و درمانی | مدیران علوم پایه | کارشناسان مدیریت پروژه | کارشناسان امور انطباق و مقررات دارویی و پزشکی | کارشناسان پژوهش‌های علوم اجتماعی | تکنسین‌های آمار | کارشناسان آمار</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان داده | مدیران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | مدیران خدمات درمانی و بهداشتی | مدیران علوم طبیعی و پایه‌ای | کارشناسان مدیریت پروژه | کارشناسان امور رگولاتوری و انطباق مقرراتی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | فیزیک | مهندسی و فناوری | اقتصاد و حسابداری | آموزش و یادگیری | مدیریت و امور اداری</t>
+          <t>ریاضیات | رایانه و الکترونیک | زبان انگلیسی | فیزیک | مهندسی و فناوری | اقتصاد و حسابداری | آموزش و پرورش | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه و مدیریت هم‌زمان وظایف | تجسم فضایی | به‌خاطرسپاری | استدلال ریاضی | محاسبات عددی | سرعت درک | تفکیک الگو و انعطاف شکل پایانی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | کارشناسان محاسبات آماری و بیم‌سنجی (اکچوئری) | ریاضیدانان | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار | کارشناسان آمار زیستی | دانشمندان علوم داده | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | تحلیل‌گران کمی مسائل مالی | دانشمندان علوم رایانه و پژوهشگران اطلاعات | برنامه‌نویسان رایانه | توسعه‌دهندگان نرم‌افزار | معماران پایگاه داده | اقتصاددانان | تحلیل‌گران سرمایه‌گذاری و مالی | کارشناسان تحلیل بازار و بازاریابی | مدیران علوم پایه | فیزیک‌دانان | مدرسان علوم ریاضی در آموزش عالی</t>
+          <t>تکنسین‌های بیوانفورماتیک | اکچوئرها و کارشناسان محاسبات فنی بیمه | ریاضی‌دانان | تحلیل‌گران تحقیق در عملیات | کارشناسان آمار | کارشناسان آمار زیستی | دانشمندان داده | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | تحلیل‌گران کمّی مالی | پژوهشگران علوم رایانه و اطلاعات | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان نرم‌افزار | معماران پایگاه داده | اقتصاددانان | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران علوم طبیعی و پایه‌ای | فیزیک‌دانان | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | سخن گفتن | ریاضیات | نظارت | علوم پایه</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | سخن گفتن | ریاضیات | نظارت | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال ریاضی | توجه انتخابی | بیان شفاهی | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | دید نزدیک | تفکیک الگو و انعطاف شکل پایانی | روانی کلام و سیالی ایده‌ها | محاسبات عددی | ابتکار و اصالت | تجسم فضایی | سرعت درک</t>
+          <t>درک کتبی | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی | توجه انتخابی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | روانی ایده‌ها | توانایی عددی | اصالت | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مهندسان زیست‌پزشکی و بیوالکتریک | دانشمندان بیوانفورماتیک | تکنسین‌های زیست‌شناسی | کارشناسان آمار زیستی | مدیران داده‌های بالینی | دانشمندان علوم رایانه و پژوهشگران اطلاعات | تکنسین‌های سیتوژنتیک | دانشمندان علوم داده | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و متخصصان سیستم‌های اطلاعات جغرافیایی GIS | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان مدارک و سوابق پزشکی | کارشناسان و تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | زیست‌شناسان سلولی و مولکولی | تکنسین‌ها و کارشناسان مهندسی فناوری نانو | مدیران علوم پایه | کارشناسان پژوهش‌های علوم اجتماعی | تکنسین‌های آمار | کارشناسان آمار</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های علوم زیستی | کارشناسان آمار زیستی | مدیران داده‌های بالینی | پژوهشگران علوم رایانه و اطلاعات | کارشناسان سیتوژنتیک | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه‌ای | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | قوانین و مقررات | مکانیک | ریاضیات | اقتصاد و حسابداری | بازاریابی و فروش | هنرهای تجسمی | فیزیک | تولید و فرآوری | آموزش و یادگیری | امور اداری و منابع انسانی</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | مکانیک | ریاضیات | اقتصاد و حسابداری | فروش و بازاریابی | هنرهای زیبا | فیزیک | تولید و فرآوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم فضایی | بیان شفاهی | بیان کتبی | روانی کلام و سیالی ایده‌ها | ابتکار و اصالت | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | دید دور | تفکیک الگو و انعطاف شکل پایانی | وضوح گفتار | تشخیص گفتار | محاسبات عددی | استدلال ریاضی | سرعت درک | توجه انتخابی | سرعت درک الگو و انسجام</t>
+          <t>تجسم | بیان شفاهی | بیان کتبی | روانی ایده‌ها | اصالت | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | بینایی دور | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | سرعت ادراکی | توجه انتخابی | سرعت بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمران | مدیران معماری و مهندسی | مدرسان معماری در آموزش عالی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | طراحان تجاری و صنعتی | مدیران ساخت‌وساز و ابنیه | بازرسان ساختمان و سازه | نقشه‌کش‌های برق و الکترونیک | مدیران تأسیسات | سرپرستان کارگاه‌های ساختمانی و استخراج | مهندسان صنایع | طراحان دکوراسیون و معماری داخلی | مهندسان معمار منظر | نیروهای فنی عمومی تعمیرات و نگهداری | کارشناسان مدیریت پروژه | مدیران نصب تأسیسات انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | متخصصان پایداری و محیط زیست | مدیران توسعه پروژه‌های انرژی بادی</t>
+          <t>نقشه‌کشان معماری و عمران | مدیران فنی و مهندسی و معماری | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | طراحان تجاری و صنعتی | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | نقشه‌کشان برق و الکترونیک | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | مهندسان صنایع | طراحان داخلی | مهندسان معمار منظر | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان مدیریت پروژه | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | کارشناسان پایداری و توسعه پایدار | مدیران توسعه پروژه‌های انرژی بادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و ساخت‌وساز | جغرافیا | زبان انگلیسی | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ایمنی و امنیت عمومی | زیست‌شناسی | مدیریت و امور اداری | قوانین و مقررات | ریاضیات | حمل‌ونقل</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | جغرافیا | زبان انگلیسی | مهندسی و فناوری | خدمات مشتری و شخصی | رایانه و الکترونیک | ایمنی و امنیت عمومی | زیست‌شناسی | مدیریت و اداره | قانون و دولت | ریاضیات | حمل و نقل</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | ابتکار و اصالت | تجسم فضایی | بیان کتبی | روانی کلام و سیالی ایده‌ها | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری در دسته‌بندی | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | تشخیص و تمایز رنگ‌ها | دید دور | محاسبات عددی | استدلال ریاضی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | اصالت | تجسم | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | بینایی دور | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کش‌های معماری و عمران | مدرسان معماری در آموزش عالی | متخصصان و مدیران احیای اراضی صنعتی رهاشده | مدیران ارشد پایداری سازمانی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مدیران ساخت‌وساز و ابنیه | برنامه‌ریزان بازسازی و احیای محیط زیست | سرپرستان کارگران فضای سبز، باغبانی و محوطه‌سازی | بوم‌شناسان صنعتی | طراحان دکوراسیون و معماری داخلی | مدیران و متخصصان مرتع‌داری | مدیران نصب تأسیسات انرژی خورشیدی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | متخصصان پایداری و محیط زیست | کارشناسان برنامه‌ریزی شهری و منطقه‌ای | متخصصان منابع آب</t>
+          <t>مهندسان کشاورزی | مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مدیران پروژه‌های ساختمانی | برنامه‌ریزان احیای محیط زیست | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | بوم‌شناسان صنعتی | طراحان داخلی | مدیران و کارشناسان مدیریت مراتع | مدیران اجرای پروژه‌های انرژی خورشیدی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان پایداری و توسعه پایدار | برنامه‌ریزان شهری و منطقه‌ای | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | شنیدن فعال | یادگیری فعال | سخن گفتن | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | یادگیری فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | درک شفاهی | استدلال استقرایی | بیان کتبی | بیان شفاهی | استدلال قیاسی | تفکیک الگو و انعطاف شکل پایانی | مرتب‌سازی اطلاعات | تجسم فضایی | دید دور | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | ابتکار و اصالت | روانی کلام و سیالی ایده‌ها | توجه انتخابی | سرعت درک | استدلال ریاضی</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | استدلال استقرایی | بیان کتبی | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | تجسم | بینایی دور | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | اصالت | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقشه‌کش‌های معماری و عمران | دانشمندان علوم جوی و فضا | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌ها و کارشناسان مهندسی عمران | دانشمندان علوم داده | متخصصان انبارهای داده | معماران پایگاه داده | نقشه‌کش‌های برق و الکترونیک | نقشه‌برداران ژئودتیک | جغرافیدانان | تکنسین‌ها و متخصصان سیستم‌های اطلاعات جغرافیایی GIS | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های آب‌شناسی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافیدانان | تکنسین‌های هیدرولوژی و آب‌شناسی | دانشمندان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | توسعه‌دهندگان نرم‌افزار | تکنسین‌های آمار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌بردار</t>
+          <t>نقشه‌کشان معماری و عمران | دانشمندان و کارشناسان علوم جوی و فضا | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی عمران | دانشمندان داده | متخصصان انباره داده | معماران پایگاه داده | نقشه‌کشان برق و الکترونیک | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | توسعه‌دهندگان نرم‌افزار | دستیاران و تکنسین‌های آمار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
